--- a/data/trans_camb/IP07_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP07_R2-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,49</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5,24</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2,23</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,8</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,31</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,33</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,49</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,14</t>
+          <t>1,5</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,27</t>
+          <t>3,29</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 5,47</t>
+          <t>-1,84; 4,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,99</t>
+          <t>-1,79; 5,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 6,91</t>
+          <t>0,29; 12,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 4,35</t>
+          <t>-0,25; 5,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 5,12</t>
+          <t>-1,46; 3,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 12,91</t>
+          <t>-1,01; 7,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 3,81</t>
+          <t>-0,39; 3,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 3,1</t>
+          <t>-0,92; 3,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 7,99</t>
+          <t>0,35; 7,87</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>60,55%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>67,72%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>238,71%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>221,45%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>79,03%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>129,96%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>60,55%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>67,72%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>234,02%</t>
+          <t>148,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>199,04%</t>
+          <t>200,62%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-57,42; —</t>
+          <t>-58,06; 610,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-60,67; 679,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>-36,36; 1391,22</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-59,67; 600,49</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-69,13; 758,01</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,04; 1415,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,57; 539,61</t>
+          <t>-21,99; 582,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,3; 407,67</t>
+          <t>-44,29; 414,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 968,76</t>
+          <t>-8,72; 985,91</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-2,74</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-2,5</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-1,7</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,28</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1,54</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,95</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,74</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,5</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,67</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 3,17</t>
+          <t>-5,13; -0,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 4,26</t>
+          <t>-4,75; -0,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 3,65</t>
+          <t>-4,07; 0,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,92; -1,1</t>
+          <t>-0,26; 3,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,87; -0,79</t>
+          <t>-0,12; 3,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 0,78</t>
+          <t>-0,52; 4,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,54</t>
+          <t>-2,07; 0,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,87</t>
+          <t>-1,9; 0,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,38</t>
+          <t>-1,89; 1,5</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-78,48%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-71,72%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-48,78%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>164,25%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>198,6%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>121,51%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-78,48%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-71,72%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-47,98%</t>
+          <t>125,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-16,84%</t>
+          <t>-16,93%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-53,38; 1175,24</t>
+          <t>-94,73; -28,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-36,01; —</t>
+          <t>-93,21; 8,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-82,1; —</t>
+          <t>-84,34; 74,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-94,94; -28,99</t>
+          <t>-49,12; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-94,2; -20,92</t>
+          <t>-43,97; 1491,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-86,8; 50,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-72,89; 50,12</t>
+          <t>-72,74; 39,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-67,83; 76,32</t>
+          <t>-68,74; 71,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-68,68; 88,77</t>
+          <t>-69,83; 101,11</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,52</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-3,16</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-3,0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,12</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,66</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,33</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,52</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-3,16</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,02</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,98</t>
+          <t>-0,97</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 3,08</t>
+          <t>-6,72; 0,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 1,77</t>
+          <t>-7,23; 0,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 4,51</t>
+          <t>-6,93; 0,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 1,12</t>
+          <t>-3,03; 2,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,16; -0,02</t>
+          <t>-3,51; 1,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 0,46</t>
+          <t>-1,62; 4,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,02</t>
+          <t>-3,64; 0,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,25</t>
+          <t>-4,16; 0,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 1,48</t>
+          <t>-3,56; 1,47</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-44,97%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-56,43%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-53,53%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>5,67%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-31,06%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>62,75%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-44,97%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-56,43%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-53,89%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-24,77%</t>
+          <t>-24,45%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-82,84; 511,84</t>
+          <t>-79,07; 40,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,17; 34,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-56,67; 689,5</t>
+          <t>-85,4; 45,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-81,77; 38,65</t>
+          <t>-86,74; 344,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-86,48; 10,91</t>
+          <t>-90,37; 272,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-83,96; 29,64</t>
+          <t>-58,24; 688,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-69,94; 42,67</t>
+          <t>-69,04; 40,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-75,83; 20,69</t>
+          <t>-78,12; 7,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-64,69; 63,26</t>
+          <t>-64,68; 66,76</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,79</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,73</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-1,11</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-0,98</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-1,04</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,98</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,79</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,73</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,19</t>
+          <t>-0,59</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>-0,87</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 1,71</t>
+          <t>-1,99; 4,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 1,85</t>
+          <t>-3,19; 2,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 8,9</t>
+          <t>-3,5; 1,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 3,81</t>
+          <t>-3,6; 1,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 1,87</t>
+          <t>-3,66; 1,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,05</t>
+          <t>-3,34; 2,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,89</t>
+          <t>-2,05; 2,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,97</t>
+          <t>-2,84; 1,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 2,94</t>
+          <t>-2,7; 0,96</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>26,98%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-24,89%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-37,85%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-32,06%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-34,17%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>32,16%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>26,98%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-24,89%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-40,32%</t>
+          <t>-19,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-5,39%</t>
+          <t>-29,15%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-83,03; 148,62</t>
+          <t>-49,2; 201,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-82,75; 136,2</t>
+          <t>-80,65; 141,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-65,62; 535,98</t>
+          <t>-79,07; 76,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-51,75; 280,26</t>
+          <t>-84,58; 128,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-79,57; 127,76</t>
+          <t>-85,27; 105,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-82,01; 87,34</t>
+          <t>-72,11; 148,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-52,96; 98,44</t>
+          <t>-52,49; 106,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-71,17; 51,68</t>
+          <t>-69,89; 58,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-58,65; 149,54</t>
+          <t>-66,23; 49,22</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,03</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,44</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-1,09</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,63</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,2</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1,46</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,03</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,44</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,08</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>-0,14</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,96</t>
+          <t>-2,51; 0,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,4</t>
+          <t>-2,99; -0,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 5,02</t>
+          <t>-2,77; 0,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 0,36</t>
+          <t>-0,6; 1,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,88; -0,09</t>
+          <t>-0,97; 1,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 0,36</t>
+          <t>-0,42; 2,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,76</t>
+          <t>-1,15; 0,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,23</t>
+          <t>-1,49; 0,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,85</t>
+          <t>-1,11; 0,85</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-29,26%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-40,83%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-30,76%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>37,05%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>11,97%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>85,63%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-29,26%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-40,83%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-30,6%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>-5,47%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,13; 159,34</t>
+          <t>-59,51; 14,7</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-41,7; 122,02</t>
+          <t>-65,92; 3,64</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 335,25</t>
+          <t>-61,76; 19,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-56,8; 16,56</t>
+          <t>-28,29; 162,32</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-66,69; -0,86</t>
+          <t>-41,59; 117,53</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-59,93; 14,89</t>
+          <t>-19,61; 218,71</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-36,37; 35,79</t>
+          <t>-36,2; 31,75</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-49,59; 12,51</t>
+          <t>-48,15; 13,67</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-31,15; 75,32</t>
+          <t>-35,58; 39,58</t>
         </is>
       </c>
     </row>
